--- a/Thesis Forecasting/PAPER CONTEXT/tables/appendix_C_rbfnn_hyperparameters.xlsx
+++ b/Thesis Forecasting/PAPER CONTEXT/tables/appendix_C_rbfnn_hyperparameters.xlsx
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>158</v>
+        <v>203</v>
       </c>
       <c r="C2" t="n">
         <v>80</v>
@@ -510,11 +510,11 @@
         <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>1.15</v>
+        <v>0.75</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Yes (-0.005794 MW)</t>
+          <t>Yes (0.043468 MW)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -540,13 +540,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>169</v>
+        <v>234</v>
       </c>
       <c r="C3" t="n">
         <v>120</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005</v>
+        <v>0.0007</v>
       </c>
       <c r="E3" t="n">
         <v>80</v>
@@ -559,7 +559,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Yes (0.002722 MW)</t>
+          <t>Yes (0.008800 MW)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>169</v>
+        <v>234</v>
       </c>
       <c r="C4" t="n">
         <v>180</v>
@@ -604,7 +604,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Yes (0.001869 MW)</t>
+          <t>Yes (0.002246 MW)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>168</v>
+        <v>213</v>
       </c>
       <c r="C5" t="n">
         <v>180</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001</v>
+        <v>0.0003</v>
       </c>
       <c r="E5" t="n">
         <v>80</v>
@@ -649,7 +649,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Yes (-0.013115 MW)</t>
+          <t>Yes (-0.020561 MW)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -675,13 +675,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>171</v>
+        <v>276</v>
       </c>
       <c r="C6" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="E6" t="n">
         <v>80</v>
@@ -690,11 +690,11 @@
         <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>1.15</v>
+        <v>0.2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Yes (-0.008944 MW)</t>
+          <t>Yes (-0.007211 MW)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>168</v>
+        <v>213</v>
       </c>
       <c r="C7" t="n">
         <v>120</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001</v>
+        <v>0.0003</v>
       </c>
       <c r="E7" t="n">
         <v>80</v>
@@ -735,11 +735,11 @@
         <v>32</v>
       </c>
       <c r="G7" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Yes (0.007462 MW)</t>
+          <t>Yes (0.007701 MW)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
